--- a/country_correlation_analysis/country_correlation_Llama_3_2-3B.xlsx
+++ b/country_correlation_analysis/country_correlation_Llama_3_2-3B.xlsx
@@ -461,7 +461,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.32314065024915</v>
+        <v>0.3231406502491499</v>
       </c>
       <c r="D2" t="n">
         <v>0.9869186054776701</v>
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.32314065024915</v>
+        <v>0.3231406502491499</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
@@ -573,7 +573,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7905226128930768</v>
+        <v>0.790522612893077</v>
       </c>
       <c r="D2" t="n">
         <v>0.1030852939487985</v>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7905226128930768</v>
+        <v>0.790522612893077</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>

--- a/country_correlation_analysis/country_correlation_Llama_3_2-3B.xlsx
+++ b/country_correlation_analysis/country_correlation_Llama_3_2-3B.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,15 +437,25 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -461,69 +471,143 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3231406502491499</v>
+        <v>0.983976556178918</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9869186054776701</v>
+        <v>0.9975027697528839</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6236645241482967</v>
+        <v>0.9887666520754099</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.9869076973201785</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.9685537465680856</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3231406502491499</v>
+        <v>0.983976556178918</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4714835677784815</v>
+        <v>0.9941120497361331</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9412864345316275</v>
+        <v>0.9462734809844001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.9423370712910379</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9086728771796849</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9869186054776701</v>
+        <v>0.9975027697528839</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4714835677784815</v>
+        <v>0.9941120497361331</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.741529986327761</v>
+        <v>0.9757409848769129</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9730519517032935</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9485626448056157</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.9887666520754099</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.9462734809844001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.9757409848769129</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9999284318028953</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9948617986910514</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.9869076973201785</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.9423370712910379</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.9730519517032935</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.9999284318028953</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9960018355086643</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>0.6236645241482967</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.9412864345316275</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.741529986327761</v>
-      </c>
-      <c r="E5" t="n">
+      <c r="B7" t="n">
+        <v>0.9685537465680856</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.9086728771796849</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.9485626448056157</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.9948617986910514</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.9960018355086643</v>
+      </c>
+      <c r="G7" t="n">
         <v>1</v>
       </c>
     </row>
@@ -538,7 +622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,15 +633,25 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
@@ -573,69 +667,143 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.790522612893077</v>
+        <v>0.1141181363714782</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1030852939487985</v>
+        <v>0.04500024033863709</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5712862881090398</v>
+        <v>0.0955118185691442</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1031283589586318</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.1600752808243315</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.790522612893077</v>
+        <v>0.1141181363714782</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6874373189442786</v>
+        <v>0.06911789603284045</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2192363247840371</v>
+        <v>0.2096299549406216</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2172464953301095</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.2741934171958086</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.1030852939487985</v>
+        <v>0.04500024033863709</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6874373189442786</v>
+        <v>0.06911789603284045</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4682009941602415</v>
+        <v>0.1405120589077806</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1481285992972695</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.2050755211629686</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.0955118185691442</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.2096299549406216</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.1405120589077806</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.007616540389480148</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.06456346225518846</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.1031283589586318</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.2172464953301095</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.1481285992972695</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.007616540389480148</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.05694692186570053</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>0.5712862881090398</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.2192363247840371</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.4682009941602415</v>
-      </c>
-      <c r="E5" t="n">
+      <c r="B7" t="n">
+        <v>0.1600752808243315</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.2741934171958086</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.2050755211629686</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.06456346225518846</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.05694692186570053</v>
+      </c>
+      <c r="G7" t="n">
         <v>0</v>
       </c>
     </row>
